--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_121_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_121_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1929,10 +1929,10 @@
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>2</v>
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>2</v>
@@ -2511,10 +2511,10 @@
         <v>15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2903,16 +2903,16 @@
         <v>32</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>11</v>
@@ -3102,13 +3102,13 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>11</v>
@@ -3827,16 +3827,16 @@
         <v>110</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>39</v>
@@ -4292,7 +4292,7 @@
         <v>4</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -4488,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5076,7 +5076,7 @@
         <v>9</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -5272,7 +5272,7 @@
         <v>13</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>2</v>
@@ -5664,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5860,10 +5860,10 @@
         <v>2</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>2</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6448,16 +6448,16 @@
         <v>27</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>4</v>
@@ -6784,16 +6784,16 @@
         <v>101</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>32</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_121_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_121_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="P2" t="n">
         <v>5</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>84.78</t>
+          <t>56.25</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>9</v>
       </c>
       <c r="N3" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>78.05</t>
+          <t>52.63</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,10 +2327,10 @@
         <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2915,14 +2915,14 @@
         <v>2</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,10 +3111,10 @@
         <v>1</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>84.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -5284,14 +5284,14 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6460,14 +6460,14 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="Y48" t="n">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="AA48" t="n">
